--- a/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 6,86</t>
+          <t>-14,32; 5,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 12,27</t>
+          <t>-2,96; 12,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 3,98</t>
+          <t>-18,02; 3,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 7,22</t>
+          <t>-21,49; 6,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 10,15</t>
+          <t>-18,5; 8,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 15,47</t>
+          <t>-3,27; 14,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 5,43</t>
+          <t>-21,75; 3,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 24,59</t>
+          <t>-42,78; 20,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,87</t>
+          <t>-10,17; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 9,94</t>
+          <t>-2,08; 9,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 1,69</t>
+          <t>-12,91; 1,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 4,51</t>
+          <t>-13,89; 3,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 11,6</t>
+          <t>-13,31; 10,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 11,94</t>
+          <t>-2,28; 11,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 2,15</t>
+          <t>-15,67; 2,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 11,16</t>
+          <t>-30,34; 10,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 9,67</t>
+          <t>-10,53; 8,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 4,34</t>
+          <t>-7,88; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 8,69</t>
+          <t>-9,45; 8,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 7,02</t>
+          <t>-9,21; 7,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 15,89</t>
+          <t>-14,99; 15,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 4,83</t>
+          <t>-8,45; 4,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 12,96</t>
+          <t>-12,28; 12,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,04; 39,73</t>
+          <t>-40,32; 42,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 15,68</t>
+          <t>-1,28; 16,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,66</t>
+          <t>-5,49; 6,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 9,99</t>
+          <t>-6,3; 10,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 8,82</t>
+          <t>-7,96; 8,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 25,98</t>
+          <t>-2,04; 26,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 7,83</t>
+          <t>-6,06; 8,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 14,81</t>
+          <t>-8,5; 15,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 33,94</t>
+          <t>-24,59; 35,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,57</t>
+          <t>-3,89; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,38</t>
+          <t>-1,04; 5,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,97</t>
+          <t>-6,77; 1,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,9</t>
+          <t>-8,75; 1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,48</t>
+          <t>-5,51; 7,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,26</t>
+          <t>-1,15; 5,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,65</t>
+          <t>-8,81; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 6,44</t>
+          <t>-24,71; 5,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 5,88</t>
+          <t>-13,36; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 12,09</t>
+          <t>-2,94; 12,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 3,07</t>
+          <t>-18,58; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 6,46</t>
+          <t>-20,12; 7,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 8,87</t>
+          <t>-17,44; 9,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 14,8</t>
+          <t>-3,07; 15,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 3,99</t>
+          <t>-22,6; 4,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 20,67</t>
+          <t>-42,13; 26,27</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 7,21</t>
+          <t>-9,53; 8,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 9,68</t>
+          <t>-1,82; 10,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 1,74</t>
+          <t>-12,81; 1,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 3,97</t>
+          <t>-13,84; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 10,59</t>
+          <t>-12,79; 12,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 11,62</t>
+          <t>-2,01; 12,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 2,23</t>
+          <t>-15,28; 2,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 10,09</t>
+          <t>-30,1; 11,78</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 8,88</t>
+          <t>-10,7; 9,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,89</t>
+          <t>-7,5; 4,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 8,54</t>
+          <t>-10,15; 7,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 7,38</t>
+          <t>-11,0; 7,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 15,01</t>
+          <t>-15,13; 16,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 4,37</t>
+          <t>-8,07; 5,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 12,56</t>
+          <t>-13,2; 11,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 42,7</t>
+          <t>-46,07; 45,58</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 16,41</t>
+          <t>-1,01; 15,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 6,92</t>
+          <t>-5,45; 6,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 10,31</t>
+          <t>-7,55; 9,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 8,73</t>
+          <t>-8,81; 8,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 26,94</t>
+          <t>-1,84; 26,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 8,2</t>
+          <t>-5,99; 8,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 15,1</t>
+          <t>-9,87; 13,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 35,31</t>
+          <t>-25,7; 32,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,29</t>
+          <t>-4,02; 5,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,12</t>
+          <t>-1,18; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,68</t>
+          <t>-6,67; 1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,73</t>
+          <t>-8,24; 1,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,88</t>
+          <t>-5,65; 8,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,97</t>
+          <t>-1,35; 6,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,28</t>
+          <t>-8,56; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 5,86</t>
+          <t>-23,78; 5,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-5,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-13,49%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 6,86</t>
+          <t>-13,47; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 12,39</t>
+          <t>-3,08; 12,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 3,5</t>
+          <t>-17,39; 3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 7,54</t>
+          <t>-19,44; 5,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 9,9</t>
+          <t>-17,22; 10,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 15,61</t>
+          <t>-3,24; 15,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 4,76</t>
+          <t>-21,5; 5,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 26,27</t>
+          <t>-41,08; 17,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-11,25%</t>
+          <t>-16,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 8,35</t>
+          <t>-9,82; 7,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 10,21</t>
+          <t>-1,84; 9,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 1,92</t>
+          <t>-12,93; 1,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 4,39</t>
+          <t>-15,96; 1,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 12,11</t>
+          <t>-13,1; 11,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 12,3</t>
+          <t>-2,07; 11,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 2,57</t>
+          <t>-15,61; 2,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 11,78</t>
+          <t>-32,69; 2,89</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,63%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 9,94</t>
+          <t>-10,77; 9,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 4,61</t>
+          <t>-8,23; 4,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 7,99</t>
+          <t>-10,02; 8,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 7,87</t>
+          <t>-6,14; 9,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 16,48</t>
+          <t>-15,42; 15,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 5,22</t>
+          <t>-8,88; 4,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 11,81</t>
+          <t>-13,4; 12,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 45,58</t>
+          <t>-24,23; 61,27</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 15,81</t>
+          <t>-1,55; 15,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,98</t>
+          <t>-5,22; 6,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 9,55</t>
+          <t>-6,38; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 8,29</t>
+          <t>-8,36; 9,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 26,23</t>
+          <t>-2,52; 25,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 8,22</t>
+          <t>-5,62; 7,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 13,94</t>
+          <t>-8,32; 14,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 32,27</t>
+          <t>-23,49; 35,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,88%</t>
+          <t>-8,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,44</t>
+          <t>-3,58; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,29</t>
+          <t>-1,15; 5,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,69</t>
+          <t>-6,82; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,77</t>
+          <t>-7,7; 1,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,22</t>
+          <t>-5,07; 8,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,15</t>
+          <t>-1,3; 6,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 2,29</t>
+          <t>-8,78; 2,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 5,78</t>
+          <t>-21,63; 6,09</t>
         </is>
       </c>
     </row>
